--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run9/epoch_80/per_file_predictions_epoch_80.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run9/epoch_80/per_file_predictions_epoch_80.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="521">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,775 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9682,0.0078,0.0034,0.0091</t>
-  </si>
-  <si>
-    <t>0.0039,0.0008,0.0005,0.9980</t>
-  </si>
-  <si>
-    <t>0.7101,0.0057,0.0008,0.3436</t>
-  </si>
-  <si>
-    <t>0.0688,0.0015,0.0009,0.9682</t>
-  </si>
-  <si>
-    <t>0.9989,0.0001,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.9953,0.0003,0.0002,0.0025</t>
-  </si>
-  <si>
-    <t>0.9944,0.0029,0.0004,0.0007</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9953,0.0015,0.0001,0.0011</t>
-  </si>
-  <si>
-    <t>0.9965,0.0011,0.0001,0.0011</t>
-  </si>
-  <si>
-    <t>0.9990,0.0004,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9972,0.0003,0.0001,0.0011</t>
-  </si>
-  <si>
-    <t>0.9475,0.0016,0.0922,0.0005</t>
-  </si>
-  <si>
-    <t>0.0445,0.0144,0.9364,0.0037</t>
-  </si>
-  <si>
-    <t>0.2473,0.0053,0.8354,0.0023</t>
-  </si>
-  <si>
-    <t>0.3343,0.0090,0.7508,0.0041</t>
-  </si>
-  <si>
-    <t>0.9361,0.0158,0.0404,0.0026</t>
-  </si>
-  <si>
-    <t>0.0025,0.9963,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.0261,0.9719,0.0030,0.0024</t>
-  </si>
-  <si>
-    <t>0.0848,0.9263,0.0012,0.0073</t>
-  </si>
-  <si>
-    <t>0.0694,0.9355,0.0019,0.0023</t>
-  </si>
-  <si>
-    <t>0.0036,0.9943,0.0017,0.0004</t>
-  </si>
-  <si>
-    <t>0.3734,0.0231,0.5864,0.0442</t>
-  </si>
-  <si>
-    <t>0.1921,0.1051,0.6330,0.0031</t>
-  </si>
-  <si>
-    <t>0.0017,0.0011,0.9934,0.0019</t>
-  </si>
-  <si>
-    <t>0.0162,0.0053,0.9654,0.0031</t>
-  </si>
-  <si>
-    <t>0.2578,0.0065,0.8653,0.0020</t>
-  </si>
-  <si>
-    <t>0.0758,0.0073,0.9289,0.0039</t>
-  </si>
-  <si>
-    <t>0.0111,0.0010,0.9886,0.0010</t>
-  </si>
-  <si>
-    <t>0.7523,0.3590,0.0034,0.0014</t>
-  </si>
-  <si>
-    <t>0.6270,0.1863,0.1310,0.0017</t>
-  </si>
-  <si>
-    <t>0.0030,0.0046,0.9967,0.0012</t>
-  </si>
-  <si>
-    <t>0.0515,0.9055,0.0500,0.0044</t>
-  </si>
-  <si>
-    <t>0.7762,0.2488,0.0250,0.0074</t>
-  </si>
-  <si>
-    <t>0.9164,0.0264,0.0392,0.0006</t>
-  </si>
-  <si>
-    <t>0.8068,0.3303,0.0021,0.0011</t>
-  </si>
-  <si>
-    <t>0.1748,0.8344,0.0492,0.0012</t>
-  </si>
-  <si>
-    <t>0.0306,0.8068,0.1281,0.0358</t>
-  </si>
-  <si>
-    <t>0.6610,0.0053,0.3004,0.0300</t>
-  </si>
-  <si>
-    <t>0.2995,0.0080,0.7835,0.0032</t>
-  </si>
-  <si>
-    <t>0.4026,0.0102,0.7181,0.0048</t>
-  </si>
-  <si>
-    <t>0.0025,0.4990,0.9857,0.0005</t>
-  </si>
-  <si>
-    <t>0.0010,0.9959,0.0011,0.0002</t>
-  </si>
-  <si>
-    <t>0.0892,0.0228,0.9243,0.0021</t>
-  </si>
-  <si>
-    <t>0.0486,0.6996,0.0087,0.7289</t>
-  </si>
-  <si>
-    <t>0.0043,0.9774,0.0054,0.0829</t>
-  </si>
-  <si>
-    <t>0.0010,0.9897,0.0503,0.0005</t>
-  </si>
-  <si>
-    <t>0.0012,0.9910,0.2496,0.0008</t>
-  </si>
-  <si>
-    <t>0.0047,0.0089,0.9860,0.0063</t>
-  </si>
-  <si>
-    <t>0.0115,0.2412,0.9759,0.0010</t>
-  </si>
-  <si>
-    <t>0.0352,0.0210,0.9467,0.0043</t>
-  </si>
-  <si>
-    <t>0.0048,0.0016,0.9929,0.0009</t>
-  </si>
-  <si>
-    <t>0.0065,0.0217,0.9776,0.0016</t>
-  </si>
-  <si>
-    <t>0.0607,0.0051,0.9496,0.0016</t>
-  </si>
-  <si>
-    <t>0.9816,0.0288,0.0018,0.0007</t>
-  </si>
-  <si>
-    <t>0.9917,0.0014,0.0015,0.0019</t>
-  </si>
-  <si>
-    <t>0.9335,0.1014,0.0067,0.0018</t>
-  </si>
-  <si>
-    <t>0.0309,0.1111,0.9668,0.0105</t>
-  </si>
-  <si>
-    <t>0.9943,0.0024,0.0009,0.0009</t>
-  </si>
-  <si>
-    <t>0.9968,0.0016,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9873,0.0147,0.0006,0.0008</t>
-  </si>
-  <si>
-    <t>0.0012,0.9424,0.9798,0.0003</t>
-  </si>
-  <si>
-    <t>0.0025,0.0018,0.9950,0.0015</t>
-  </si>
-  <si>
-    <t>0.0046,0.0054,0.9891,0.0034</t>
-  </si>
-  <si>
-    <t>0.0009,0.8833,0.9883,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.0006,0.9972,0.0024</t>
-  </si>
-  <si>
-    <t>0.0042,0.9904,0.0048,0.0001</t>
-  </si>
-  <si>
-    <t>0.0127,0.9839,0.0073,0.0003</t>
-  </si>
-  <si>
-    <t>0.5873,0.0110,0.6585,0.0019</t>
-  </si>
-  <si>
-    <t>0.7243,0.0399,0.3439,0.0088</t>
-  </si>
-  <si>
-    <t>0.0238,0.0063,0.9719,0.0039</t>
-  </si>
-  <si>
-    <t>0.0024,0.9083,0.9267,0.0008</t>
-  </si>
-  <si>
-    <t>0.0016,0.8641,0.9521,0.0003</t>
-  </si>
-  <si>
-    <t>0.0075,0.9825,0.0283,0.0003</t>
-  </si>
-  <si>
-    <t>0.0029,0.9808,0.1201,0.0014</t>
-  </si>
-  <si>
-    <t>0.0047,0.0004,0.0224,0.9876</t>
-  </si>
-  <si>
-    <t>0.0048,0.0071,0.0014,0.9960</t>
-  </si>
-  <si>
-    <t>0.0042,0.0003,0.0001,0.9987</t>
-  </si>
-  <si>
-    <t>0.0090,0.0039,0.0036,0.9930</t>
-  </si>
-  <si>
-    <t>0.0127,0.0006,0.0018,0.9933</t>
-  </si>
-  <si>
-    <t>0.0043,0.0015,0.0009,0.9973</t>
-  </si>
-  <si>
-    <t>0.0002,0.9975,0.4480,0.0001</t>
-  </si>
-  <si>
-    <t>0.0027,0.4141,0.9883,0.0012</t>
-  </si>
-  <si>
-    <t>0.0068,0.6270,0.7894,0.0058</t>
-  </si>
-  <si>
-    <t>0.0100,0.3188,0.9555,0.0028</t>
-  </si>
-  <si>
-    <t>0.0014,0.9867,0.1789,0.0002</t>
-  </si>
-  <si>
-    <t>0.0034,0.9631,0.4685,0.0004</t>
-  </si>
-  <si>
-    <t>0.9980,0.0004,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9936,0.0035,0.0005,0.0008</t>
-  </si>
-  <si>
-    <t>0.9931,0.0036,0.0003,0.0009</t>
-  </si>
-  <si>
-    <t>0.9896,0.0062,0.0021,0.0012</t>
-  </si>
-  <si>
-    <t>0.9892,0.0055,0.0008,0.0025</t>
-  </si>
-  <si>
-    <t>0.9941,0.0013,0.0002,0.0020</t>
-  </si>
-  <si>
-    <t>0.9959,0.0012,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.9950,0.0040,0.0009,0.0004</t>
-  </si>
-  <si>
-    <t>0.9986,0.0004,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9987,0.0003,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9965,0.0014,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0002,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9965,0.0012,0.0002,0.0007</t>
-  </si>
-  <si>
-    <t>0.9949,0.0022,0.0002,0.0010</t>
-  </si>
-  <si>
-    <t>0.9986,0.0001,0.0000,0.0005</t>
-  </si>
-  <si>
-    <t>0.0045,0.0039,0.9913,0.0038</t>
-  </si>
-  <si>
-    <t>0.1118,0.0075,0.9345,0.0007</t>
-  </si>
-  <si>
-    <t>0.9764,0.0016,0.0164,0.0025</t>
-  </si>
-  <si>
-    <t>0.0037,0.0013,0.9906,0.0026</t>
-  </si>
-  <si>
-    <t>0.0414,0.9610,0.0013,0.0066</t>
-  </si>
-  <si>
-    <t>0.0158,0.9786,0.0063,0.0029</t>
-  </si>
-  <si>
-    <t>0.0169,0.9809,0.0028,0.0042</t>
-  </si>
-  <si>
-    <t>0.0347,0.9626,0.0114,0.0015</t>
-  </si>
-  <si>
-    <t>0.0047,0.9919,0.0016,0.0005</t>
-  </si>
-  <si>
-    <t>0.0128,0.9855,0.0015,0.0024</t>
-  </si>
-  <si>
-    <t>0.8519,0.2589,0.0017,0.0007</t>
-  </si>
-  <si>
-    <t>0.9227,0.0044,0.0920,0.0018</t>
-  </si>
-  <si>
-    <t>0.1313,0.0156,0.8583,0.0276</t>
-  </si>
-  <si>
-    <t>0.4273,0.0155,0.6397,0.0050</t>
-  </si>
-  <si>
-    <t>0.8059,0.0098,0.2726,0.0015</t>
-  </si>
-  <si>
-    <t>0.0042,0.0730,0.0023,0.9873</t>
-  </si>
-  <si>
-    <t>0.0011,0.9957,0.0176,0.0008</t>
-  </si>
-  <si>
-    <t>0.0013,0.9860,0.1279,0.0042</t>
-  </si>
-  <si>
-    <t>0.0001,0.9983,0.0009,0.0088</t>
-  </si>
-  <si>
-    <t>0.0007,0.9472,0.9658,0.0004</t>
-  </si>
-  <si>
-    <t>0.0181,0.9789,0.0136,0.0012</t>
-  </si>
-  <si>
-    <t>0.8134,0.2686,0.0085,0.0003</t>
-  </si>
-  <si>
-    <t>0.8589,0.1805,0.0333,0.0048</t>
-  </si>
-  <si>
-    <t>0.9921,0.0018,0.0007,0.0023</t>
-  </si>
-  <si>
-    <t>0.9881,0.0071,0.0010,0.0025</t>
-  </si>
-  <si>
-    <t>0.9983,0.0004,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9915,0.0023,0.0022,0.0013</t>
-  </si>
-  <si>
-    <t>0.9986,0.0003,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9942,0.0020,0.0018,0.0005</t>
-  </si>
-  <si>
-    <t>0.9844,0.0032,0.0024,0.0063</t>
-  </si>
-  <si>
-    <t>0.9824,0.0041,0.0010,0.0068</t>
-  </si>
-  <si>
-    <t>0.0167,0.5230,0.9376,0.0026</t>
-  </si>
-  <si>
-    <t>0.0695,0.0751,0.8526,0.0029</t>
-  </si>
-  <si>
-    <t>0.0274,0.0943,0.9057,0.0006</t>
-  </si>
-  <si>
-    <t>0.1465,0.0779,0.6547,0.0005</t>
-  </si>
-  <si>
-    <t>0.9885,0.0017,0.0048,0.0012</t>
-  </si>
-  <si>
-    <t>0.7787,0.0053,0.3467,0.0018</t>
-  </si>
-  <si>
-    <t>0.4608,0.0010,0.7992,0.0004</t>
-  </si>
-  <si>
-    <t>0.7158,0.0076,0.3261,0.0085</t>
-  </si>
-  <si>
-    <t>0.0207,0.0019,0.0087,0.9853</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0002,0.9999</t>
-  </si>
-  <si>
-    <t>0.0049,0.0055,0.0018,0.9956</t>
-  </si>
-  <si>
-    <t>0.0022,0.0002,0.0003,0.9990</t>
-  </si>
-  <si>
-    <t>0.0064,0.9510,0.1265,0.0025</t>
-  </si>
-  <si>
-    <t>0.9954,0.0026,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.0516,0.9419,0.0041,0.0060</t>
-  </si>
-  <si>
-    <t>0.9947,0.0012,0.0005,0.0013</t>
-  </si>
-  <si>
-    <t>0.8827,0.1245,0.0106,0.0020</t>
-  </si>
-  <si>
-    <t>0.9808,0.0013,0.0011,0.0093</t>
-  </si>
-  <si>
-    <t>0.9825,0.0011,0.0010,0.0106</t>
-  </si>
-  <si>
-    <t>0.9938,0.0028,0.0008,0.0007</t>
-  </si>
-  <si>
-    <t>0.0083,0.0656,0.8469,0.2483</t>
-  </si>
-  <si>
-    <t>0.9558,0.0038,0.0023,0.0244</t>
-  </si>
-  <si>
-    <t>0.9623,0.0009,0.0003,0.0393</t>
-  </si>
-  <si>
-    <t>0.1505,0.8795,0.0038,0.0038</t>
-  </si>
-  <si>
-    <t>0.9246,0.0096,0.0531,0.0078</t>
-  </si>
-  <si>
-    <t>0.9602,0.0215,0.0111,0.0036</t>
-  </si>
-  <si>
-    <t>0.6484,0.2718,0.0092,0.0336</t>
-  </si>
-  <si>
-    <t>0.9310,0.0337,0.0214,0.0049</t>
-  </si>
-  <si>
-    <t>0.9537,0.0186,0.0227,0.0009</t>
-  </si>
-  <si>
-    <t>0.9927,0.0048,0.0015,0.0005</t>
-  </si>
-  <si>
-    <t>0.9962,0.0009,0.0011,0.0003</t>
-  </si>
-  <si>
-    <t>0.9963,0.0015,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.9978,0.0003,0.0001,0.0008</t>
-  </si>
-  <si>
-    <t>0.9947,0.0010,0.0005,0.0016</t>
-  </si>
-  <si>
-    <t>0.9862,0.0099,0.0016,0.0017</t>
-  </si>
-  <si>
-    <t>0.9955,0.0014,0.0003,0.0008</t>
-  </si>
-  <si>
-    <t>0.9973,0.0002,0.0001,0.0010</t>
-  </si>
-  <si>
-    <t>0.9118,0.1255,0.0031,0.0035</t>
-  </si>
-  <si>
-    <t>0.0667,0.9532,0.0010,0.0011</t>
-  </si>
-  <si>
-    <t>0.8949,0.1788,0.0050,0.0019</t>
-  </si>
-  <si>
-    <t>0.0591,0.3941,0.9382,0.0155</t>
-  </si>
-  <si>
-    <t>0.9954,0.0048,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9894,0.0078,0.0009,0.0008</t>
-  </si>
-  <si>
-    <t>0.9956,0.0020,0.0009,0.0003</t>
-  </si>
-  <si>
-    <t>0.9831,0.0180,0.0011,0.0013</t>
-  </si>
-  <si>
-    <t>0.0080,0.0250,0.9900,0.0016</t>
-  </si>
-  <si>
-    <t>0.9695,0.0117,0.0167,0.0005</t>
-  </si>
-  <si>
-    <t>0.0009,0.0070,0.9942,0.0004</t>
-  </si>
-  <si>
-    <t>0.0377,0.0061,0.9704,0.0013</t>
-  </si>
-  <si>
-    <t>0.0126,0.0021,0.9845,0.0004</t>
-  </si>
-  <si>
-    <t>0.0013,0.0022,0.9967,0.0012</t>
-  </si>
-  <si>
-    <t>0.0023,0.0009,0.9919,0.0033</t>
-  </si>
-  <si>
-    <t>0.0138,0.0039,0.9843,0.0007</t>
-  </si>
-  <si>
-    <t>0.0016,0.0022,0.9972,0.0011</t>
-  </si>
-  <si>
-    <t>0.3282,0.0430,0.6936,0.0061</t>
-  </si>
-  <si>
-    <t>0.0211,0.0043,0.9747,0.0029</t>
-  </si>
-  <si>
-    <t>0.0997,0.0093,0.8901,0.0119</t>
-  </si>
-  <si>
-    <t>0.1091,0.2124,0.6435,0.0108</t>
-  </si>
-  <si>
-    <t>0.1396,0.6652,0.1899,0.0027</t>
-  </si>
-  <si>
-    <t>0.2673,0.0111,0.7618,0.0008</t>
-  </si>
-  <si>
-    <t>0.1133,0.1104,0.7268,0.0274</t>
-  </si>
-  <si>
-    <t>0.8400,0.0391,0.1056,0.0029</t>
-  </si>
-  <si>
-    <t>0.9527,0.0961,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.8413,0.3736,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9950,0.0052,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9726,0.0369,0.0010,0.0018</t>
-  </si>
-  <si>
-    <t>0.9450,0.0632,0.0099,0.0029</t>
-  </si>
-  <si>
-    <t>0.7401,0.0507,0.2271,0.0213</t>
-  </si>
-  <si>
-    <t>0.9664,0.0020,0.0432,0.0007</t>
-  </si>
-  <si>
-    <t>0.9658,0.0052,0.0125,0.0067</t>
-  </si>
-  <si>
-    <t>0.7993,0.0233,0.2049,0.0031</t>
-  </si>
-  <si>
-    <t>0.5534,0.0118,0.5510,0.0073</t>
-  </si>
-  <si>
-    <t>0.0185,0.0076,0.9408,0.0062</t>
-  </si>
-  <si>
-    <t>0.0063,0.0205,0.9620,0.0062</t>
-  </si>
-  <si>
-    <t>0.0059,0.0360,0.9839,0.0016</t>
-  </si>
-  <si>
-    <t>0.1673,0.0064,0.8617,0.0012</t>
-  </si>
-  <si>
-    <t>0.0371,0.0679,0.9538,0.0010</t>
-  </si>
-  <si>
-    <t>0.9966,0.0003,0.0000,0.0016</t>
-  </si>
-  <si>
-    <t>0.9971,0.0004,0.0002,0.0007</t>
-  </si>
-  <si>
-    <t>0.9942,0.0024,0.0009,0.0008</t>
-  </si>
-  <si>
-    <t>0.9953,0.0015,0.0005,0.0010</t>
-  </si>
-  <si>
-    <t>0.9799,0.0215,0.0020,0.0014</t>
-  </si>
-  <si>
-    <t>0.9939,0.0020,0.0007,0.0012</t>
-  </si>
-  <si>
-    <t>0.9930,0.0045,0.0009,0.0007</t>
-  </si>
-  <si>
-    <t>0.9956,0.0011,0.0002,0.0010</t>
-  </si>
-  <si>
-    <t>0.0401,0.3893,0.9198,0.0071</t>
-  </si>
-  <si>
-    <t>0.0323,0.0631,0.9215,0.0201</t>
-  </si>
-  <si>
-    <t>0.9775,0.0098,0.0077,0.0017</t>
-  </si>
-  <si>
-    <t>0.0076,0.0101,0.9894,0.0014</t>
-  </si>
-  <si>
-    <t>0.0008,0.0025,0.9947,0.0023</t>
-  </si>
-  <si>
-    <t>0.0386,0.0375,0.8807,0.0005</t>
-  </si>
-  <si>
-    <t>0.0047,0.0009,0.9942,0.0005</t>
-  </si>
-  <si>
-    <t>0.0387,0.0105,0.9348,0.0018</t>
-  </si>
-  <si>
-    <t>0.0005,0.0049,0.9969,0.0024</t>
-  </si>
-  <si>
-    <t>0.0039,0.0056,0.9908,0.0003</t>
-  </si>
-  <si>
-    <t>0.0202,0.0138,0.9219,0.0351</t>
-  </si>
-  <si>
-    <t>0.9542,0.0052,0.0255,0.0097</t>
-  </si>
-  <si>
-    <t>0.4579,0.0015,0.5361,0.0122</t>
-  </si>
-  <si>
-    <t>0.9804,0.0022,0.0141,0.0013</t>
-  </si>
-  <si>
-    <t>0.9859,0.0092,0.0005,0.0024</t>
-  </si>
-  <si>
-    <t>0.9914,0.0087,0.0005,0.0007</t>
-  </si>
-  <si>
-    <t>0.9977,0.0011,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9840,0.0130,0.0036,0.0016</t>
-  </si>
-  <si>
-    <t>0.9989,0.0003,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9908,0.0122,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.9957,0.0010,0.0007,0.0007</t>
-  </si>
-  <si>
-    <t>0.9989,0.0002,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.0110,0.0095,0.9746,0.0012</t>
-  </si>
-  <si>
-    <t>0.0020,0.0129,0.9941,0.0009</t>
-  </si>
-  <si>
-    <t>0.0127,0.6540,0.7417,0.0031</t>
-  </si>
-  <si>
-    <t>0.0544,0.0582,0.8646,0.0083</t>
-  </si>
-  <si>
-    <t>0.0293,0.0016,0.9844,0.0002</t>
-  </si>
-  <si>
-    <t>0.2629,0.0425,0.5312,0.2642</t>
-  </si>
-  <si>
-    <t>0.0329,0.0064,0.9546,0.0047</t>
-  </si>
-  <si>
-    <t>0.0182,0.0030,0.9792,0.0014</t>
-  </si>
-  <si>
-    <t>0.9328,0.0013,0.0027,0.1071</t>
-  </si>
-  <si>
-    <t>0.0060,0.0256,0.0052,0.9901</t>
-  </si>
-  <si>
-    <t>0.1061,0.0004,0.0040,0.9493</t>
-  </si>
-  <si>
-    <t>0.0100,0.0001,0.0000,0.9975</t>
-  </si>
-  <si>
-    <t>0.0029,0.0001,0.0003,0.9988</t>
-  </si>
-  <si>
-    <t>0.5400,0.0280,0.0297,0.5085</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.9766,0.0018,0.0066,0.0057</t>
+  </si>
+  <si>
+    <t>0.0476,0.0011,0.0009,0.9861</t>
+  </si>
+  <si>
+    <t>0.9437,0.0021,0.0007,0.0544</t>
+  </si>
+  <si>
+    <t>0.0150,0.0014,0.0003,0.9940</t>
+  </si>
+  <si>
+    <t>0.9980,0.0009,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9956,0.0001,0.0000,0.0046</t>
+  </si>
+  <si>
+    <t>0.9974,0.0017,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9980,0.0005,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9933,0.0016,0.0003,0.0023</t>
+  </si>
+  <si>
+    <t>0.9969,0.0004,0.0002,0.0011</t>
+  </si>
+  <si>
+    <t>0.9980,0.0005,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9242,0.0155,0.0279,0.0118</t>
+  </si>
+  <si>
+    <t>0.1118,0.0142,0.9001,0.0088</t>
+  </si>
+  <si>
+    <t>0.6529,0.0071,0.5565,0.0021</t>
+  </si>
+  <si>
+    <t>0.0341,0.0017,0.9604,0.0016</t>
+  </si>
+  <si>
+    <t>0.9410,0.0200,0.0250,0.0009</t>
+  </si>
+  <si>
+    <t>0.0198,0.9825,0.0011,0.0005</t>
+  </si>
+  <si>
+    <t>0.0058,0.9883,0.0025,0.0020</t>
+  </si>
+  <si>
+    <t>0.0271,0.9791,0.0010,0.0013</t>
+  </si>
+  <si>
+    <t>0.2013,0.8658,0.0015,0.0006</t>
+  </si>
+  <si>
+    <t>0.0063,0.9889,0.0023,0.0009</t>
+  </si>
+  <si>
+    <t>0.9232,0.0050,0.0545,0.0081</t>
+  </si>
+  <si>
+    <t>0.7270,0.0072,0.3436,0.0056</t>
+  </si>
+  <si>
+    <t>0.0090,0.0011,0.9893,0.0006</t>
+  </si>
+  <si>
+    <t>0.0652,0.0074,0.9187,0.0026</t>
+  </si>
+  <si>
+    <t>0.0417,0.0026,0.9716,0.0013</t>
+  </si>
+  <si>
+    <t>0.0205,0.0096,0.9653,0.0058</t>
+  </si>
+  <si>
+    <t>0.0023,0.0007,0.9945,0.0010</t>
+  </si>
+  <si>
+    <t>0.8486,0.1987,0.0052,0.0005</t>
+  </si>
+  <si>
+    <t>0.7505,0.0919,0.1405,0.0022</t>
+  </si>
+  <si>
+    <t>0.0089,0.0119,0.9851,0.0086</t>
+  </si>
+  <si>
+    <t>0.1044,0.7195,0.1945,0.0020</t>
+  </si>
+  <si>
+    <t>0.8804,0.0356,0.0239,0.0412</t>
+  </si>
+  <si>
+    <t>0.9685,0.0077,0.0202,0.0023</t>
+  </si>
+  <si>
+    <t>0.6934,0.4252,0.0093,0.0021</t>
+  </si>
+  <si>
+    <t>0.1548,0.8723,0.0828,0.0032</t>
+  </si>
+  <si>
+    <t>0.0089,0.0690,0.8709,0.0735</t>
+  </si>
+  <si>
+    <t>0.1879,0.0051,0.7553,0.0249</t>
+  </si>
+  <si>
+    <t>0.0540,0.0542,0.9482,0.0082</t>
+  </si>
+  <si>
+    <t>0.2946,0.0004,0.5235,0.0126</t>
+  </si>
+  <si>
+    <t>0.0044,0.0106,0.9821,0.0039</t>
+  </si>
+  <si>
+    <t>0.0002,0.9992,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0812,0.0075,0.9339,0.0044</t>
+  </si>
+  <si>
+    <t>0.0022,0.8962,0.0016,0.8597</t>
+  </si>
+  <si>
+    <t>0.0753,0.8808,0.0533,0.0208</t>
+  </si>
+  <si>
+    <t>0.0029,0.9826,0.1649,0.0008</t>
+  </si>
+  <si>
+    <t>0.0018,0.9889,0.0902,0.0021</t>
+  </si>
+  <si>
+    <t>0.0031,0.0030,0.9928,0.0009</t>
+  </si>
+  <si>
+    <t>0.0129,0.5268,0.9400,0.0024</t>
+  </si>
+  <si>
+    <t>0.0089,0.0029,0.9866,0.0025</t>
+  </si>
+  <si>
+    <t>0.0064,0.0020,0.9852,0.0068</t>
+  </si>
+  <si>
+    <t>0.0010,0.0200,0.9876,0.0007</t>
+  </si>
+  <si>
+    <t>0.0122,0.0054,0.9699,0.0029</t>
+  </si>
+  <si>
+    <t>0.9811,0.0291,0.0005,0.0008</t>
+  </si>
+  <si>
+    <t>0.9938,0.0026,0.0013,0.0006</t>
+  </si>
+  <si>
+    <t>0.9927,0.0034,0.0008,0.0013</t>
+  </si>
+  <si>
+    <t>0.0231,0.0592,0.9800,0.0086</t>
+  </si>
+  <si>
+    <t>0.9947,0.0044,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9849,0.0084,0.0056,0.0010</t>
+  </si>
+  <si>
+    <t>0.9842,0.0205,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.0127,0.7628,0.9086,0.0034</t>
+  </si>
+  <si>
+    <t>0.0032,0.0078,0.9877,0.0074</t>
+  </si>
+  <si>
+    <t>0.0274,0.0239,0.9694,0.0070</t>
+  </si>
+  <si>
+    <t>0.0011,0.8945,0.9890,0.0004</t>
+  </si>
+  <si>
+    <t>0.0003,0.0009,0.9985,0.0006</t>
+  </si>
+  <si>
+    <t>0.0034,0.9930,0.0017,0.0001</t>
+  </si>
+  <si>
+    <t>0.0339,0.9647,0.0062,0.0003</t>
+  </si>
+  <si>
+    <t>0.9753,0.0022,0.0287,0.0012</t>
+  </si>
+  <si>
+    <t>0.0734,0.0681,0.9083,0.0425</t>
+  </si>
+  <si>
+    <t>0.0197,0.0103,0.9574,0.0011</t>
+  </si>
+  <si>
+    <t>0.0128,0.9292,0.3825,0.0019</t>
+  </si>
+  <si>
+    <t>0.0105,0.7962,0.8370,0.0010</t>
+  </si>
+  <si>
+    <t>0.0074,0.9738,0.1969,0.0014</t>
+  </si>
+  <si>
+    <t>0.0059,0.8849,0.7488,0.0025</t>
+  </si>
+  <si>
+    <t>0.0071,0.0044,0.0076,0.9917</t>
+  </si>
+  <si>
+    <t>0.0002,0.0027,0.0002,0.9997</t>
+  </si>
+  <si>
+    <t>0.0110,0.0004,0.0004,0.9963</t>
+  </si>
+  <si>
+    <t>0.0480,0.0043,0.0018,0.9817</t>
+  </si>
+  <si>
+    <t>0.0170,0.0007,0.0013,0.9922</t>
+  </si>
+  <si>
+    <t>0.0067,0.0043,0.0004,0.9960</t>
+  </si>
+  <si>
+    <t>0.0019,0.9587,0.9318,0.0006</t>
+  </si>
+  <si>
+    <t>0.0031,0.6225,0.9748,0.0018</t>
+  </si>
+  <si>
+    <t>0.0132,0.5580,0.7787,0.0022</t>
+  </si>
+  <si>
+    <t>0.0123,0.3196,0.9762,0.0020</t>
+  </si>
+  <si>
+    <t>0.0005,0.9961,0.0208,0.0000</t>
+  </si>
+  <si>
+    <t>0.0020,0.9654,0.8233,0.0006</t>
+  </si>
+  <si>
+    <t>0.9989,0.0001,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9924,0.0052,0.0014,0.0006</t>
+  </si>
+  <si>
+    <t>0.9891,0.0055,0.0007,0.0020</t>
+  </si>
+  <si>
+    <t>0.9904,0.0026,0.0005,0.0035</t>
+  </si>
+  <si>
+    <t>0.9914,0.0047,0.0003,0.0013</t>
+  </si>
+  <si>
+    <t>0.9931,0.0008,0.0004,0.0032</t>
+  </si>
+  <si>
+    <t>0.9961,0.0022,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.9919,0.0070,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.9972,0.0003,0.0001,0.0012</t>
+  </si>
+  <si>
+    <t>0.9982,0.0004,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9966,0.0020,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9979,0.0001,0.0001,0.0011</t>
+  </si>
+  <si>
+    <t>0.9904,0.0076,0.0020,0.0010</t>
+  </si>
+  <si>
+    <t>0.9937,0.0020,0.0004,0.0015</t>
+  </si>
+  <si>
+    <t>0.9984,0.0002,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.0082,0.0009,0.9907,0.0011</t>
+  </si>
+  <si>
+    <t>0.0239,0.0215,0.9672,0.0014</t>
+  </si>
+  <si>
+    <t>0.9418,0.0292,0.0082,0.0082</t>
+  </si>
+  <si>
+    <t>0.0059,0.0024,0.9911,0.0012</t>
+  </si>
+  <si>
+    <t>0.0411,0.9633,0.0009,0.0041</t>
+  </si>
+  <si>
+    <t>0.0063,0.9918,0.0013,0.0009</t>
+  </si>
+  <si>
+    <t>0.0090,0.9894,0.0018,0.0045</t>
+  </si>
+  <si>
+    <t>0.1430,0.8747,0.0195,0.0014</t>
+  </si>
+  <si>
+    <t>0.0025,0.9954,0.0006,0.0008</t>
+  </si>
+  <si>
+    <t>0.0227,0.9802,0.0028,0.0023</t>
+  </si>
+  <si>
+    <t>0.9254,0.1242,0.0020,0.0026</t>
+  </si>
+  <si>
+    <t>0.3011,0.0487,0.6682,0.0041</t>
+  </si>
+  <si>
+    <t>0.5019,0.0076,0.6512,0.0072</t>
+  </si>
+  <si>
+    <t>0.2519,0.0068,0.7916,0.0027</t>
+  </si>
+  <si>
+    <t>0.8801,0.0351,0.0502,0.0296</t>
+  </si>
+  <si>
+    <t>0.1427,0.3134,0.0872,0.7163</t>
+  </si>
+  <si>
+    <t>0.0005,0.9970,0.0023,0.0022</t>
+  </si>
+  <si>
+    <t>0.0007,0.9902,0.0693,0.0036</t>
+  </si>
+  <si>
+    <t>0.0031,0.9893,0.0060,0.0072</t>
+  </si>
+  <si>
+    <t>0.0014,0.9837,0.8205,0.0005</t>
+  </si>
+  <si>
+    <t>0.0040,0.9917,0.0101,0.0005</t>
+  </si>
+  <si>
+    <t>0.9455,0.1007,0.0022,0.0004</t>
+  </si>
+  <si>
+    <t>0.9346,0.0817,0.0057,0.0016</t>
+  </si>
+  <si>
+    <t>0.9964,0.0011,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9921,0.0030,0.0015,0.0019</t>
+  </si>
+  <si>
+    <t>0.9938,0.0012,0.0006,0.0020</t>
+  </si>
+  <si>
+    <t>0.9946,0.0014,0.0006,0.0011</t>
+  </si>
+  <si>
+    <t>0.9957,0.0009,0.0005,0.0009</t>
+  </si>
+  <si>
+    <t>0.9987,0.0003,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9920,0.0004,0.0002,0.0057</t>
+  </si>
+  <si>
+    <t>0.9933,0.0014,0.0008,0.0018</t>
+  </si>
+  <si>
+    <t>0.0013,0.9332,0.9637,0.0003</t>
+  </si>
+  <si>
+    <t>0.0135,0.1568,0.9221,0.0010</t>
+  </si>
+  <si>
+    <t>0.0181,0.0070,0.9667,0.0004</t>
+  </si>
+  <si>
+    <t>0.0111,0.0095,0.9857,0.0002</t>
+  </si>
+  <si>
+    <t>0.9746,0.0038,0.0105,0.0021</t>
+  </si>
+  <si>
+    <t>0.7753,0.0068,0.2970,0.0052</t>
+  </si>
+  <si>
+    <t>0.0799,0.0009,0.9569,0.0014</t>
+  </si>
+  <si>
+    <t>0.4074,0.0391,0.6430,0.0052</t>
+  </si>
+  <si>
+    <t>0.0160,0.0005,0.0016,0.9931</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.0002,0.9996</t>
+  </si>
+  <si>
+    <t>0.0028,0.0056,0.0028,0.9962</t>
+  </si>
+  <si>
+    <t>0.0031,0.0006,0.0005,0.9982</t>
+  </si>
+  <si>
+    <t>0.0094,0.9703,0.0375,0.0003</t>
+  </si>
+  <si>
+    <t>0.9950,0.0052,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.6197,0.5050,0.0038,0.0029</t>
+  </si>
+  <si>
+    <t>0.9932,0.0025,0.0003,0.0016</t>
+  </si>
+  <si>
+    <t>0.8605,0.2306,0.0027,0.0010</t>
+  </si>
+  <si>
+    <t>0.9945,0.0004,0.0012,0.0010</t>
+  </si>
+  <si>
+    <t>0.9720,0.0006,0.0019,0.0203</t>
+  </si>
+  <si>
+    <t>0.9922,0.0015,0.0018,0.0013</t>
+  </si>
+  <si>
+    <t>0.0058,0.2308,0.7483,0.2001</t>
+  </si>
+  <si>
+    <t>0.8798,0.0012,0.0034,0.1684</t>
+  </si>
+  <si>
+    <t>0.9672,0.0014,0.0004,0.0302</t>
+  </si>
+  <si>
+    <t>0.5975,0.5032,0.0043,0.0049</t>
+  </si>
+  <si>
+    <t>0.9710,0.0219,0.0049,0.0010</t>
+  </si>
+  <si>
+    <t>0.9665,0.0196,0.0089,0.0021</t>
+  </si>
+  <si>
+    <t>0.2931,0.6930,0.0864,0.0091</t>
+  </si>
+  <si>
+    <t>0.9038,0.0259,0.0847,0.0036</t>
+  </si>
+  <si>
+    <t>0.9635,0.0064,0.0266,0.0011</t>
+  </si>
+  <si>
+    <t>0.9936,0.0006,0.0004,0.0033</t>
+  </si>
+  <si>
+    <t>0.9893,0.0036,0.0017,0.0026</t>
+  </si>
+  <si>
+    <t>0.9965,0.0010,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9864,0.0053,0.0047,0.0016</t>
+  </si>
+  <si>
+    <t>0.9944,0.0023,0.0009,0.0009</t>
+  </si>
+  <si>
+    <t>0.9955,0.0012,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9985,0.0001,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9544,0.0609,0.0019,0.0013</t>
+  </si>
+  <si>
+    <t>0.4256,0.6672,0.0031,0.0040</t>
+  </si>
+  <si>
+    <t>0.2290,0.8287,0.0009,0.0027</t>
+  </si>
+  <si>
+    <t>0.6076,0.3535,0.1231,0.0140</t>
+  </si>
+  <si>
+    <t>0.9958,0.0039,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9872,0.0099,0.0010,0.0011</t>
+  </si>
+  <si>
+    <t>0.9856,0.0289,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.9561,0.0617,0.0013,0.0014</t>
+  </si>
+  <si>
+    <t>0.0052,0.2484,0.9860,0.0043</t>
+  </si>
+  <si>
+    <t>0.9859,0.0044,0.0071,0.0009</t>
+  </si>
+  <si>
+    <t>0.0036,0.0018,0.9922,0.0006</t>
+  </si>
+  <si>
+    <t>0.0072,0.0147,0.9895,0.0008</t>
+  </si>
+  <si>
+    <t>0.0025,0.0022,0.9922,0.0038</t>
+  </si>
+  <si>
+    <t>0.0006,0.0010,0.9963,0.0031</t>
+  </si>
+  <si>
+    <t>0.0046,0.0027,0.9875,0.0035</t>
+  </si>
+  <si>
+    <t>0.0045,0.0043,0.9938,0.0008</t>
+  </si>
+  <si>
+    <t>0.0205,0.0021,0.9760,0.0007</t>
+  </si>
+  <si>
+    <t>0.0594,0.0025,0.9441,0.0011</t>
+  </si>
+  <si>
+    <t>0.0230,0.0079,0.9703,0.0066</t>
+  </si>
+  <si>
+    <t>0.1417,0.0182,0.8481,0.0084</t>
+  </si>
+  <si>
+    <t>0.7028,0.0776,0.1486,0.0010</t>
+  </si>
+  <si>
+    <t>0.1767,0.0535,0.7686,0.0025</t>
+  </si>
+  <si>
+    <t>0.7474,0.0213,0.2696,0.0017</t>
+  </si>
+  <si>
+    <t>0.8665,0.0693,0.0494,0.0072</t>
+  </si>
+  <si>
+    <t>0.1182,0.0154,0.8750,0.0032</t>
+  </si>
+  <si>
+    <t>0.7710,0.4179,0.0019,0.0003</t>
+  </si>
+  <si>
+    <t>0.9663,0.0797,0.0007,0.0008</t>
+  </si>
+  <si>
+    <t>0.9888,0.0208,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.8581,0.2361,0.0023,0.0030</t>
+  </si>
+  <si>
+    <t>0.9202,0.1098,0.0026,0.0041</t>
+  </si>
+  <si>
+    <t>0.9171,0.0179,0.0462,0.0119</t>
+  </si>
+  <si>
+    <t>0.9750,0.0037,0.0170,0.0012</t>
+  </si>
+  <si>
+    <t>0.9825,0.0035,0.0054,0.0025</t>
+  </si>
+  <si>
+    <t>0.6684,0.0182,0.4668,0.0044</t>
+  </si>
+  <si>
+    <t>0.7498,0.0106,0.2345,0.0148</t>
+  </si>
+  <si>
+    <t>0.0014,0.0037,0.9842,0.0061</t>
+  </si>
+  <si>
+    <t>0.0344,0.2389,0.8762,0.0415</t>
+  </si>
+  <si>
+    <t>0.0110,0.0146,0.9892,0.0009</t>
+  </si>
+  <si>
+    <t>0.4094,0.0091,0.6747,0.0025</t>
+  </si>
+  <si>
+    <t>0.0107,0.0134,0.9762,0.0018</t>
+  </si>
+  <si>
+    <t>0.9980,0.0003,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9969,0.0011,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9970,0.0005,0.0001,0.0011</t>
+  </si>
+  <si>
+    <t>0.9979,0.0013,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9946,0.0019,0.0004,0.0010</t>
+  </si>
+  <si>
+    <t>0.9450,0.0700,0.0007,0.0028</t>
+  </si>
+  <si>
+    <t>0.9913,0.0039,0.0007,0.0020</t>
+  </si>
+  <si>
+    <t>0.9980,0.0005,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.0555,0.0101,0.9542,0.0054</t>
+  </si>
+  <si>
+    <t>0.0698,0.1609,0.7937,0.0017</t>
+  </si>
+  <si>
+    <t>0.9624,0.0025,0.0314,0.0015</t>
+  </si>
+  <si>
+    <t>0.0017,0.0018,0.9950,0.0008</t>
+  </si>
+  <si>
+    <t>0.0012,0.0061,0.9946,0.0022</t>
+  </si>
+  <si>
+    <t>0.0070,0.0335,0.9756,0.0014</t>
+  </si>
+  <si>
+    <t>0.0164,0.0049,0.9837,0.0009</t>
+  </si>
+  <si>
+    <t>0.0123,0.0562,0.8891,0.0077</t>
+  </si>
+  <si>
+    <t>0.0018,0.0033,0.9942,0.0040</t>
+  </si>
+  <si>
+    <t>0.0012,0.0041,0.9936,0.0012</t>
+  </si>
+  <si>
+    <t>0.0048,0.0074,0.9726,0.0055</t>
+  </si>
+  <si>
+    <t>0.9562,0.0024,0.0528,0.0035</t>
+  </si>
+  <si>
+    <t>0.3758,0.0017,0.7343,0.0018</t>
+  </si>
+  <si>
+    <t>0.9584,0.0045,0.0307,0.0040</t>
+  </si>
+  <si>
+    <t>0.9899,0.0065,0.0011,0.0013</t>
+  </si>
+  <si>
+    <t>0.9947,0.0019,0.0015,0.0004</t>
+  </si>
+  <si>
+    <t>0.9962,0.0022,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9938,0.0045,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.9970,0.0004,0.0000,0.0010</t>
+  </si>
+  <si>
+    <t>0.9943,0.0038,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9919,0.0073,0.0018,0.0003</t>
+  </si>
+  <si>
+    <t>0.9960,0.0005,0.0001,0.0020</t>
+  </si>
+  <si>
+    <t>0.0488,0.0571,0.9187,0.0026</t>
+  </si>
+  <si>
+    <t>0.0035,0.2142,0.9737,0.0009</t>
+  </si>
+  <si>
+    <t>0.0042,0.0260,0.9697,0.0030</t>
+  </si>
+  <si>
+    <t>0.0056,0.0885,0.9285,0.0200</t>
+  </si>
+  <si>
+    <t>0.0031,0.0022,0.9944,0.0008</t>
+  </si>
+  <si>
+    <t>0.6802,0.0063,0.2243,0.0348</t>
+  </si>
+  <si>
+    <t>0.0132,0.0059,0.9804,0.0021</t>
+  </si>
+  <si>
+    <t>0.1764,0.0062,0.8090,0.0168</t>
+  </si>
+  <si>
+    <t>0.8685,0.0023,0.0010,0.2053</t>
+  </si>
+  <si>
+    <t>0.0089,0.0139,0.0048,0.9904</t>
+  </si>
+  <si>
+    <t>0.3079,0.0007,0.0020,0.8758</t>
+  </si>
+  <si>
+    <t>0.0072,0.0000,0.0001,0.9984</t>
+  </si>
+  <si>
+    <t>0.0082,0.0001,0.0003,0.9971</t>
+  </si>
+  <si>
+    <t>0.9048,0.0066,0.0102,0.0749</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1962,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1976,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1987,7 +1990,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2004,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2018,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2032,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2046,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2060,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2074,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2088,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2102,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2116,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2130,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2144,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,10 +2155,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2172,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2186,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2200,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2214,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2228,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2242,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2256,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,10 +2267,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,10 +2281,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2298,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2312,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2326,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2340,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2354,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2365,7 +2368,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2379,7 +2382,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2396,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2410,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2424,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2435,7 +2438,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2449,7 +2452,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2466,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,10 +2477,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,10 +2491,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2508,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2522,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2536,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2550,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2564,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2575,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2592,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2606,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2620,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2634,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,10 +2645,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2662,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2676,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2690,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2704,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2718,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2732,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2746,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2760,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2774,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2788,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2802,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2816,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2830,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2844,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2858,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2872,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2886,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2900,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,10 +2911,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,10 +2925,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2942,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,10 +2953,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2970,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2984,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,10 +2995,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3012,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3026,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3040,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3054,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3068,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3082,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,10 +3093,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,10 +3107,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3121,7 +3124,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,7 +3138,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3152,7 @@
         <v>262</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,10 +3163,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3180,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3194,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3208,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3222,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3236,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3250,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3264,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3278,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3292,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3306,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3320,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3334,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3348,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3362,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3376,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3390,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3404,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3418,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3432,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3446,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3460,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3474,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3488,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3502,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3516,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3530,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3541,7 +3544,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,10 +3555,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,10 +3569,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3583,7 +3586,7 @@
         <v>261</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3597,7 +3600,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3611,7 +3614,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3628,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3642,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3656,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3670,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3684,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,7 +3698,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3709,7 +3712,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3726,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3740,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3754,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3768,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3782,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3796,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3810,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3824,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3835,7 +3838,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3849,7 +3852,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3866,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3880,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3894,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,7 +3908,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,7 +3922,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,10 +3933,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3950,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3964,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3978,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3992,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,7 +4006,7 @@
         <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4020,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,10 +4031,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4048,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4059,7 +4062,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4076,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4087,7 +4090,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4104,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4118,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4132,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4146,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,10 +4157,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4174,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4188,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,10 +4199,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4216,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4230,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4244,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4258,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4272,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4286,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>277</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4300,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4314,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4328,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4342,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4353,7 +4356,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4367,7 +4370,7 @@
         <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,10 +4381,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,10 +4395,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4412,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4426,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4440,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4454,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4468,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4482,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4496,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4510,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4524,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4538,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4552,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4566,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4580,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,7 +4594,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4608,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4619,7 +4622,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,10 +4633,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,10 +4647,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,10 +4661,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,10 +4675,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,10 +4689,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4706,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4717,7 +4720,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4734,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4748,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4759,7 +4762,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4773,7 +4776,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4790,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4804,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4815,7 +4818,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,10 +4829,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4846,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4860,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4874,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4888,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4902,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4916,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4930,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4944,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4958,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4972,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4986,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5000,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5014,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5028,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5039,7 +5042,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5056,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5070,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5084,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5098,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5112,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5126,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5140,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5154,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5168,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,7 +5182,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5193,7 +5196,7 @@
         <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5210,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5224,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5238,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5252,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5266,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5280,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5294,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5308,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5322,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5336,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5350,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,10 +5361,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5378,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5392,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,10 +5403,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5420,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5434,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5445,7 +5448,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5462,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5476,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5490,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5504,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,10 +5515,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
   </sheetData>
